--- a/backend/data/07_AUDITORIA.xlsx
+++ b/backend/data/07_AUDITORIA.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="536">
   <si>
     <t>ID_LOG</t>
   </si>
@@ -1530,6 +1530,69 @@
   </si>
   <si>
     <t>LOG_000235</t>
+  </si>
+  <si>
+    <t>LOG_000236</t>
+  </si>
+  <si>
+    <t>18:14:29</t>
+  </si>
+  <si>
+    <t>PRO_000006</t>
+  </si>
+  <si>
+    <t>LOG_000237</t>
+  </si>
+  <si>
+    <t>19:28:30</t>
+  </si>
+  <si>
+    <t>PRO_000007</t>
+  </si>
+  <si>
+    <t>LOG_000238</t>
+  </si>
+  <si>
+    <t>19:28:51</t>
+  </si>
+  <si>
+    <t>Responsaveis</t>
+  </si>
+  <si>
+    <t>RES_000001</t>
+  </si>
+  <si>
+    <t>LOG_000239</t>
+  </si>
+  <si>
+    <t>ResponsaveisFinanceiros</t>
+  </si>
+  <si>
+    <t>AR_000001</t>
+  </si>
+  <si>
+    <t>LOG_000240</t>
+  </si>
+  <si>
+    <t>19:29:32</t>
+  </si>
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>Respons�vel Teste Smoke</t>
+  </si>
+  <si>
+    <t>Responsável Financeiro Acentuação Ção</t>
+  </si>
+  <si>
+    <t>LOG_000241</t>
+  </si>
+  <si>
+    <t>19:30:02</t>
+  </si>
+  <si>
+    <t>LOG_000242</t>
   </si>
   <si>
     <t>ID_LOG_ACESSO</t>
@@ -1941,7 +2004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L235"/>
+  <dimension ref="A1:L242"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10871,6 +10934,272 @@
         <v>482</v>
       </c>
       <c r="L235" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>505</v>
+      </c>
+      <c r="B236" s="2">
+        <v>46278.885061064815</v>
+      </c>
+      <c r="C236" t="s">
+        <v>506</v>
+      </c>
+      <c r="D236" t="s">
+        <v>372</v>
+      </c>
+      <c r="E236" t="s">
+        <v>15</v>
+      </c>
+      <c r="F236" t="s">
+        <v>26</v>
+      </c>
+      <c r="G236" t="s">
+        <v>379</v>
+      </c>
+      <c r="H236" t="s">
+        <v>507</v>
+      </c>
+      <c r="I236" t="s">
+        <v>19</v>
+      </c>
+      <c r="J236" t="s">
+        <v>19</v>
+      </c>
+      <c r="K236" t="s">
+        <v>19</v>
+      </c>
+      <c r="L236" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>508</v>
+      </c>
+      <c r="B237" s="2">
+        <v>46278.93646758102</v>
+      </c>
+      <c r="C237" t="s">
+        <v>509</v>
+      </c>
+      <c r="D237" t="s">
+        <v>372</v>
+      </c>
+      <c r="E237" t="s">
+        <v>15</v>
+      </c>
+      <c r="F237" t="s">
+        <v>26</v>
+      </c>
+      <c r="G237" t="s">
+        <v>379</v>
+      </c>
+      <c r="H237" t="s">
+        <v>510</v>
+      </c>
+      <c r="I237" t="s">
+        <v>19</v>
+      </c>
+      <c r="J237" t="s">
+        <v>19</v>
+      </c>
+      <c r="K237" t="s">
+        <v>19</v>
+      </c>
+      <c r="L237" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>511</v>
+      </c>
+      <c r="B238" s="2">
+        <v>46278.936704733795</v>
+      </c>
+      <c r="C238" t="s">
+        <v>512</v>
+      </c>
+      <c r="D238" t="s">
+        <v>372</v>
+      </c>
+      <c r="E238" t="s">
+        <v>15</v>
+      </c>
+      <c r="F238" t="s">
+        <v>16</v>
+      </c>
+      <c r="G238" t="s">
+        <v>513</v>
+      </c>
+      <c r="H238" t="s">
+        <v>514</v>
+      </c>
+      <c r="I238" t="s">
+        <v>19</v>
+      </c>
+      <c r="J238" t="s">
+        <v>19</v>
+      </c>
+      <c r="K238" t="s">
+        <v>19</v>
+      </c>
+      <c r="L238" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>515</v>
+      </c>
+      <c r="B239" s="2">
+        <v>46278.93670796296</v>
+      </c>
+      <c r="C239" t="s">
+        <v>512</v>
+      </c>
+      <c r="D239" t="s">
+        <v>372</v>
+      </c>
+      <c r="E239" t="s">
+        <v>15</v>
+      </c>
+      <c r="F239" t="s">
+        <v>16</v>
+      </c>
+      <c r="G239" t="s">
+        <v>516</v>
+      </c>
+      <c r="H239" t="s">
+        <v>517</v>
+      </c>
+      <c r="I239" t="s">
+        <v>19</v>
+      </c>
+      <c r="J239" t="s">
+        <v>19</v>
+      </c>
+      <c r="K239" t="s">
+        <v>19</v>
+      </c>
+      <c r="L239" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>518</v>
+      </c>
+      <c r="B240" s="2">
+        <v>46278.93717721065</v>
+      </c>
+      <c r="C240" t="s">
+        <v>519</v>
+      </c>
+      <c r="D240" t="s">
+        <v>372</v>
+      </c>
+      <c r="E240" t="s">
+        <v>366</v>
+      </c>
+      <c r="F240" t="s">
+        <v>16</v>
+      </c>
+      <c r="G240" t="s">
+        <v>513</v>
+      </c>
+      <c r="H240" t="s">
+        <v>514</v>
+      </c>
+      <c r="I240" t="s">
+        <v>520</v>
+      </c>
+      <c r="J240" t="s">
+        <v>521</v>
+      </c>
+      <c r="K240" t="s">
+        <v>522</v>
+      </c>
+      <c r="L240" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>523</v>
+      </c>
+      <c r="B241" s="2">
+        <v>46278.93752895833</v>
+      </c>
+      <c r="C241" t="s">
+        <v>524</v>
+      </c>
+      <c r="D241" t="s">
+        <v>372</v>
+      </c>
+      <c r="E241" t="s">
+        <v>366</v>
+      </c>
+      <c r="F241" t="s">
+        <v>16</v>
+      </c>
+      <c r="G241" t="s">
+        <v>516</v>
+      </c>
+      <c r="H241" t="s">
+        <v>517</v>
+      </c>
+      <c r="I241" t="s">
+        <v>367</v>
+      </c>
+      <c r="J241" t="s">
+        <v>368</v>
+      </c>
+      <c r="K241" t="s">
+        <v>369</v>
+      </c>
+      <c r="L241" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>525</v>
+      </c>
+      <c r="B242" s="2">
+        <v>46278.93753063657</v>
+      </c>
+      <c r="C242" t="s">
+        <v>524</v>
+      </c>
+      <c r="D242" t="s">
+        <v>372</v>
+      </c>
+      <c r="E242" t="s">
+        <v>366</v>
+      </c>
+      <c r="F242" t="s">
+        <v>16</v>
+      </c>
+      <c r="G242" t="s">
+        <v>513</v>
+      </c>
+      <c r="H242" t="s">
+        <v>514</v>
+      </c>
+      <c r="I242" t="s">
+        <v>367</v>
+      </c>
+      <c r="J242" t="s">
+        <v>368</v>
+      </c>
+      <c r="K242" t="s">
+        <v>369</v>
+      </c>
+      <c r="L242" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10887,7 +11216,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10915,7 +11244,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10924,13 +11253,13 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -10946,7 +11275,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10955,7 +11284,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -10971,7 +11300,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10980,10 +11309,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/backend/data/07_AUDITORIA.xlsx
+++ b/backend/data/07_AUDITORIA.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="544">
   <si>
     <t>ID_LOG</t>
   </si>
@@ -1593,6 +1593,30 @@
   </si>
   <si>
     <t>LOG_000242</t>
+  </si>
+  <si>
+    <t>LOG_000243</t>
+  </si>
+  <si>
+    <t>20:01:58</t>
+  </si>
+  <si>
+    <t>ALU_000003</t>
+  </si>
+  <si>
+    <t>LOG_000244</t>
+  </si>
+  <si>
+    <t>20:02:24</t>
+  </si>
+  <si>
+    <t>NEG_000003</t>
+  </si>
+  <si>
+    <t>LOG_000245</t>
+  </si>
+  <si>
+    <t>PRO_000008</t>
   </si>
   <si>
     <t>ID_LOG_ACESSO</t>
@@ -2004,7 +2028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L242"/>
+  <dimension ref="A1:L245"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11200,6 +11224,120 @@
         <v>369</v>
       </c>
       <c r="L242" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>526</v>
+      </c>
+      <c r="B243" s="2">
+        <v>46278.95970673611</v>
+      </c>
+      <c r="C243" t="s">
+        <v>527</v>
+      </c>
+      <c r="D243" t="s">
+        <v>372</v>
+      </c>
+      <c r="E243" t="s">
+        <v>15</v>
+      </c>
+      <c r="F243" t="s">
+        <v>16</v>
+      </c>
+      <c r="G243" t="s">
+        <v>373</v>
+      </c>
+      <c r="H243" t="s">
+        <v>528</v>
+      </c>
+      <c r="I243" t="s">
+        <v>19</v>
+      </c>
+      <c r="J243" t="s">
+        <v>19</v>
+      </c>
+      <c r="K243" t="s">
+        <v>19</v>
+      </c>
+      <c r="L243" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>529</v>
+      </c>
+      <c r="B244" s="2">
+        <v>46278.96000670139</v>
+      </c>
+      <c r="C244" t="s">
+        <v>530</v>
+      </c>
+      <c r="D244" t="s">
+        <v>372</v>
+      </c>
+      <c r="E244" t="s">
+        <v>15</v>
+      </c>
+      <c r="F244" t="s">
+        <v>26</v>
+      </c>
+      <c r="G244" t="s">
+        <v>376</v>
+      </c>
+      <c r="H244" t="s">
+        <v>531</v>
+      </c>
+      <c r="I244" t="s">
+        <v>19</v>
+      </c>
+      <c r="J244" t="s">
+        <v>19</v>
+      </c>
+      <c r="K244" t="s">
+        <v>19</v>
+      </c>
+      <c r="L244" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>532</v>
+      </c>
+      <c r="B245" s="2">
+        <v>46278.960007835645</v>
+      </c>
+      <c r="C245" t="s">
+        <v>530</v>
+      </c>
+      <c r="D245" t="s">
+        <v>372</v>
+      </c>
+      <c r="E245" t="s">
+        <v>15</v>
+      </c>
+      <c r="F245" t="s">
+        <v>26</v>
+      </c>
+      <c r="G245" t="s">
+        <v>379</v>
+      </c>
+      <c r="H245" t="s">
+        <v>533</v>
+      </c>
+      <c r="I245" t="s">
+        <v>19</v>
+      </c>
+      <c r="J245" t="s">
+        <v>19</v>
+      </c>
+      <c r="K245" t="s">
+        <v>19</v>
+      </c>
+      <c r="L245" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11216,7 +11354,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11244,7 +11382,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11253,13 +11391,13 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -11275,7 +11413,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11284,7 +11422,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -11300,7 +11438,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11309,10 +11447,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>

--- a/backend/data/07_AUDITORIA.xlsx
+++ b/backend/data/07_AUDITORIA.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="558">
   <si>
     <t>ID_LOG</t>
   </si>
@@ -1617,6 +1617,48 @@
   </si>
   <si>
     <t>PRO_000008</t>
+  </si>
+  <si>
+    <t>LOG_000246</t>
+  </si>
+  <si>
+    <t>12:59:02</t>
+  </si>
+  <si>
+    <t>ALU_000004</t>
+  </si>
+  <si>
+    <t>LOG_000247</t>
+  </si>
+  <si>
+    <t>RES_000002</t>
+  </si>
+  <si>
+    <t>LOG_000248</t>
+  </si>
+  <si>
+    <t>12:59:03</t>
+  </si>
+  <si>
+    <t>AR_000002</t>
+  </si>
+  <si>
+    <t>LOG_000249</t>
+  </si>
+  <si>
+    <t>12:59:28</t>
+  </si>
+  <si>
+    <t>NEG_000004</t>
+  </si>
+  <si>
+    <t>LOG_000250</t>
+  </si>
+  <si>
+    <t>12:59:29</t>
+  </si>
+  <si>
+    <t>PRO_000009</t>
   </si>
   <si>
     <t>ID_LOG_ACESSO</t>
@@ -2028,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L245"/>
+  <dimension ref="A1:L250"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11338,6 +11380,196 @@
         <v>19</v>
       </c>
       <c r="L245" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>534</v>
+      </c>
+      <c r="B246" s="2">
+        <v>46280.666003680555</v>
+      </c>
+      <c r="C246" t="s">
+        <v>535</v>
+      </c>
+      <c r="D246" t="s">
+        <v>372</v>
+      </c>
+      <c r="E246" t="s">
+        <v>15</v>
+      </c>
+      <c r="F246" t="s">
+        <v>16</v>
+      </c>
+      <c r="G246" t="s">
+        <v>373</v>
+      </c>
+      <c r="H246" t="s">
+        <v>536</v>
+      </c>
+      <c r="I246" t="s">
+        <v>19</v>
+      </c>
+      <c r="J246" t="s">
+        <v>19</v>
+      </c>
+      <c r="K246" t="s">
+        <v>19</v>
+      </c>
+      <c r="L246" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>537</v>
+      </c>
+      <c r="B247" s="2">
+        <v>46280.66600590278</v>
+      </c>
+      <c r="C247" t="s">
+        <v>535</v>
+      </c>
+      <c r="D247" t="s">
+        <v>372</v>
+      </c>
+      <c r="E247" t="s">
+        <v>15</v>
+      </c>
+      <c r="F247" t="s">
+        <v>16</v>
+      </c>
+      <c r="G247" t="s">
+        <v>513</v>
+      </c>
+      <c r="H247" t="s">
+        <v>538</v>
+      </c>
+      <c r="I247" t="s">
+        <v>19</v>
+      </c>
+      <c r="J247" t="s">
+        <v>19</v>
+      </c>
+      <c r="K247" t="s">
+        <v>19</v>
+      </c>
+      <c r="L247" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>539</v>
+      </c>
+      <c r="B248" s="2">
+        <v>46280.66600898148</v>
+      </c>
+      <c r="C248" t="s">
+        <v>540</v>
+      </c>
+      <c r="D248" t="s">
+        <v>372</v>
+      </c>
+      <c r="E248" t="s">
+        <v>15</v>
+      </c>
+      <c r="F248" t="s">
+        <v>16</v>
+      </c>
+      <c r="G248" t="s">
+        <v>516</v>
+      </c>
+      <c r="H248" t="s">
+        <v>541</v>
+      </c>
+      <c r="I248" t="s">
+        <v>19</v>
+      </c>
+      <c r="J248" t="s">
+        <v>19</v>
+      </c>
+      <c r="K248" t="s">
+        <v>19</v>
+      </c>
+      <c r="L248" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>542</v>
+      </c>
+      <c r="B249" s="2">
+        <v>46280.66630618056</v>
+      </c>
+      <c r="C249" t="s">
+        <v>543</v>
+      </c>
+      <c r="D249" t="s">
+        <v>372</v>
+      </c>
+      <c r="E249" t="s">
+        <v>15</v>
+      </c>
+      <c r="F249" t="s">
+        <v>26</v>
+      </c>
+      <c r="G249" t="s">
+        <v>376</v>
+      </c>
+      <c r="H249" t="s">
+        <v>544</v>
+      </c>
+      <c r="I249" t="s">
+        <v>19</v>
+      </c>
+      <c r="J249" t="s">
+        <v>19</v>
+      </c>
+      <c r="K249" t="s">
+        <v>19</v>
+      </c>
+      <c r="L249" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>545</v>
+      </c>
+      <c r="B250" s="2">
+        <v>46280.66630916667</v>
+      </c>
+      <c r="C250" t="s">
+        <v>546</v>
+      </c>
+      <c r="D250" t="s">
+        <v>372</v>
+      </c>
+      <c r="E250" t="s">
+        <v>15</v>
+      </c>
+      <c r="F250" t="s">
+        <v>26</v>
+      </c>
+      <c r="G250" t="s">
+        <v>379</v>
+      </c>
+      <c r="H250" t="s">
+        <v>547</v>
+      </c>
+      <c r="I250" t="s">
+        <v>19</v>
+      </c>
+      <c r="J250" t="s">
+        <v>19</v>
+      </c>
+      <c r="K250" t="s">
+        <v>19</v>
+      </c>
+      <c r="L250" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11354,7 +11586,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11382,7 +11614,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11391,13 +11623,13 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -11413,7 +11645,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11422,7 +11654,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -11438,7 +11670,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11447,10 +11679,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/backend/data/07_AUDITORIA.xlsx
+++ b/backend/data/07_AUDITORIA.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3057" uniqueCount="622">
   <si>
     <t>ID_LOG</t>
   </si>
@@ -1659,6 +1659,198 @@
   </si>
   <si>
     <t>PRO_000009</t>
+  </si>
+  <si>
+    <t>LOG_000251</t>
+  </si>
+  <si>
+    <t>17:31:42</t>
+  </si>
+  <si>
+    <t>seed-precos</t>
+  </si>
+  <si>
+    <t>SER_000052</t>
+  </si>
+  <si>
+    <t>LOG_000252</t>
+  </si>
+  <si>
+    <t>17:31:43</t>
+  </si>
+  <si>
+    <t>TPR_000052</t>
+  </si>
+  <si>
+    <t>LOG_000253</t>
+  </si>
+  <si>
+    <t>17:31:44</t>
+  </si>
+  <si>
+    <t>SER_000053</t>
+  </si>
+  <si>
+    <t>LOG_000254</t>
+  </si>
+  <si>
+    <t>TPR_000053</t>
+  </si>
+  <si>
+    <t>LOG_000255</t>
+  </si>
+  <si>
+    <t>17:31:45</t>
+  </si>
+  <si>
+    <t>SER_000054</t>
+  </si>
+  <si>
+    <t>LOG_000256</t>
+  </si>
+  <si>
+    <t>TPR_000054</t>
+  </si>
+  <si>
+    <t>LOG_000257</t>
+  </si>
+  <si>
+    <t>SER_000055</t>
+  </si>
+  <si>
+    <t>LOG_000258</t>
+  </si>
+  <si>
+    <t>17:31:47</t>
+  </si>
+  <si>
+    <t>TPR_000055</t>
+  </si>
+  <si>
+    <t>LOG_000259</t>
+  </si>
+  <si>
+    <t>SER_000056</t>
+  </si>
+  <si>
+    <t>LOG_000260</t>
+  </si>
+  <si>
+    <t>TPR_000056</t>
+  </si>
+  <si>
+    <t>LOG_000261</t>
+  </si>
+  <si>
+    <t>SER_000057</t>
+  </si>
+  <si>
+    <t>LOG_000262</t>
+  </si>
+  <si>
+    <t>TPR_000057</t>
+  </si>
+  <si>
+    <t>LOG_000263</t>
+  </si>
+  <si>
+    <t>17:31:48</t>
+  </si>
+  <si>
+    <t>SER_000058</t>
+  </si>
+  <si>
+    <t>LOG_000264</t>
+  </si>
+  <si>
+    <t>TPR_000058</t>
+  </si>
+  <si>
+    <t>LOG_000265</t>
+  </si>
+  <si>
+    <t>SER_000059</t>
+  </si>
+  <si>
+    <t>LOG_000266</t>
+  </si>
+  <si>
+    <t>17:31:49</t>
+  </si>
+  <si>
+    <t>TPR_000059</t>
+  </si>
+  <si>
+    <t>LOG_000267</t>
+  </si>
+  <si>
+    <t>SER_000060</t>
+  </si>
+  <si>
+    <t>LOG_000268</t>
+  </si>
+  <si>
+    <t>17:31:50</t>
+  </si>
+  <si>
+    <t>TPR_000060</t>
+  </si>
+  <si>
+    <t>LOG_000269</t>
+  </si>
+  <si>
+    <t>SER_000061</t>
+  </si>
+  <si>
+    <t>LOG_000270</t>
+  </si>
+  <si>
+    <t>TPR_000061</t>
+  </si>
+  <si>
+    <t>LOG_000271</t>
+  </si>
+  <si>
+    <t>17:31:51</t>
+  </si>
+  <si>
+    <t>SER_000062</t>
+  </si>
+  <si>
+    <t>LOG_000272</t>
+  </si>
+  <si>
+    <t>17:31:52</t>
+  </si>
+  <si>
+    <t>TPR_000062</t>
+  </si>
+  <si>
+    <t>LOG_000273</t>
+  </si>
+  <si>
+    <t>SER_000063</t>
+  </si>
+  <si>
+    <t>LOG_000274</t>
+  </si>
+  <si>
+    <t>TPR_000063</t>
+  </si>
+  <si>
+    <t>LOG_000275</t>
+  </si>
+  <si>
+    <t>SER_000064</t>
+  </si>
+  <si>
+    <t>LOG_000276</t>
+  </si>
+  <si>
+    <t>17:31:53</t>
+  </si>
+  <si>
+    <t>TPR_000064</t>
   </si>
   <si>
     <t>ID_LOG_ACESSO</t>
@@ -2070,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L250"/>
+  <dimension ref="A1:L276"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11570,6 +11762,994 @@
         <v>19</v>
       </c>
       <c r="L250" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>548</v>
+      </c>
+      <c r="B251" s="2">
+        <v>46280.8553522338</v>
+      </c>
+      <c r="C251" t="s">
+        <v>549</v>
+      </c>
+      <c r="D251" t="s">
+        <v>550</v>
+      </c>
+      <c r="E251" t="s">
+        <v>15</v>
+      </c>
+      <c r="F251" t="s">
+        <v>16</v>
+      </c>
+      <c r="G251" t="s">
+        <v>152</v>
+      </c>
+      <c r="H251" t="s">
+        <v>551</v>
+      </c>
+      <c r="I251" t="s">
+        <v>19</v>
+      </c>
+      <c r="J251" t="s">
+        <v>19</v>
+      </c>
+      <c r="K251" t="s">
+        <v>19</v>
+      </c>
+      <c r="L251" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>552</v>
+      </c>
+      <c r="B252" s="2">
+        <v>46280.85535886574</v>
+      </c>
+      <c r="C252" t="s">
+        <v>553</v>
+      </c>
+      <c r="D252" t="s">
+        <v>550</v>
+      </c>
+      <c r="E252" t="s">
+        <v>15</v>
+      </c>
+      <c r="F252" t="s">
+        <v>142</v>
+      </c>
+      <c r="G252" t="s">
+        <v>155</v>
+      </c>
+      <c r="H252" t="s">
+        <v>554</v>
+      </c>
+      <c r="I252" t="s">
+        <v>19</v>
+      </c>
+      <c r="J252" t="s">
+        <v>19</v>
+      </c>
+      <c r="K252" t="s">
+        <v>19</v>
+      </c>
+      <c r="L252" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>555</v>
+      </c>
+      <c r="B253" s="2">
+        <v>46280.85537085649</v>
+      </c>
+      <c r="C253" t="s">
+        <v>556</v>
+      </c>
+      <c r="D253" t="s">
+        <v>550</v>
+      </c>
+      <c r="E253" t="s">
+        <v>15</v>
+      </c>
+      <c r="F253" t="s">
+        <v>16</v>
+      </c>
+      <c r="G253" t="s">
+        <v>152</v>
+      </c>
+      <c r="H253" t="s">
+        <v>557</v>
+      </c>
+      <c r="I253" t="s">
+        <v>19</v>
+      </c>
+      <c r="J253" t="s">
+        <v>19</v>
+      </c>
+      <c r="K253" t="s">
+        <v>19</v>
+      </c>
+      <c r="L253" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>558</v>
+      </c>
+      <c r="B254" s="2">
+        <v>46280.85538143518</v>
+      </c>
+      <c r="C254" t="s">
+        <v>556</v>
+      </c>
+      <c r="D254" t="s">
+        <v>550</v>
+      </c>
+      <c r="E254" t="s">
+        <v>15</v>
+      </c>
+      <c r="F254" t="s">
+        <v>142</v>
+      </c>
+      <c r="G254" t="s">
+        <v>155</v>
+      </c>
+      <c r="H254" t="s">
+        <v>559</v>
+      </c>
+      <c r="I254" t="s">
+        <v>19</v>
+      </c>
+      <c r="J254" t="s">
+        <v>19</v>
+      </c>
+      <c r="K254" t="s">
+        <v>19</v>
+      </c>
+      <c r="L254" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>560</v>
+      </c>
+      <c r="B255" s="2">
+        <v>46280.85538540509</v>
+      </c>
+      <c r="C255" t="s">
+        <v>561</v>
+      </c>
+      <c r="D255" t="s">
+        <v>550</v>
+      </c>
+      <c r="E255" t="s">
+        <v>15</v>
+      </c>
+      <c r="F255" t="s">
+        <v>16</v>
+      </c>
+      <c r="G255" t="s">
+        <v>152</v>
+      </c>
+      <c r="H255" t="s">
+        <v>562</v>
+      </c>
+      <c r="I255" t="s">
+        <v>19</v>
+      </c>
+      <c r="J255" t="s">
+        <v>19</v>
+      </c>
+      <c r="K255" t="s">
+        <v>19</v>
+      </c>
+      <c r="L255" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>563</v>
+      </c>
+      <c r="B256" s="2">
+        <v>46280.855388310185</v>
+      </c>
+      <c r="C256" t="s">
+        <v>561</v>
+      </c>
+      <c r="D256" t="s">
+        <v>550</v>
+      </c>
+      <c r="E256" t="s">
+        <v>15</v>
+      </c>
+      <c r="F256" t="s">
+        <v>142</v>
+      </c>
+      <c r="G256" t="s">
+        <v>155</v>
+      </c>
+      <c r="H256" t="s">
+        <v>564</v>
+      </c>
+      <c r="I256" t="s">
+        <v>19</v>
+      </c>
+      <c r="J256" t="s">
+        <v>19</v>
+      </c>
+      <c r="K256" t="s">
+        <v>19</v>
+      </c>
+      <c r="L256" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>565</v>
+      </c>
+      <c r="B257" s="2">
+        <v>46280.855391875</v>
+      </c>
+      <c r="C257" t="s">
+        <v>561</v>
+      </c>
+      <c r="D257" t="s">
+        <v>550</v>
+      </c>
+      <c r="E257" t="s">
+        <v>15</v>
+      </c>
+      <c r="F257" t="s">
+        <v>16</v>
+      </c>
+      <c r="G257" t="s">
+        <v>152</v>
+      </c>
+      <c r="H257" t="s">
+        <v>566</v>
+      </c>
+      <c r="I257" t="s">
+        <v>19</v>
+      </c>
+      <c r="J257" t="s">
+        <v>19</v>
+      </c>
+      <c r="K257" t="s">
+        <v>19</v>
+      </c>
+      <c r="L257" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>567</v>
+      </c>
+      <c r="B258" s="2">
+        <v>46280.85540568287</v>
+      </c>
+      <c r="C258" t="s">
+        <v>568</v>
+      </c>
+      <c r="D258" t="s">
+        <v>550</v>
+      </c>
+      <c r="E258" t="s">
+        <v>15</v>
+      </c>
+      <c r="F258" t="s">
+        <v>142</v>
+      </c>
+      <c r="G258" t="s">
+        <v>155</v>
+      </c>
+      <c r="H258" t="s">
+        <v>569</v>
+      </c>
+      <c r="I258" t="s">
+        <v>19</v>
+      </c>
+      <c r="J258" t="s">
+        <v>19</v>
+      </c>
+      <c r="K258" t="s">
+        <v>19</v>
+      </c>
+      <c r="L258" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>570</v>
+      </c>
+      <c r="B259" s="2">
+        <v>46280.8554083912</v>
+      </c>
+      <c r="C259" t="s">
+        <v>568</v>
+      </c>
+      <c r="D259" t="s">
+        <v>550</v>
+      </c>
+      <c r="E259" t="s">
+        <v>15</v>
+      </c>
+      <c r="F259" t="s">
+        <v>16</v>
+      </c>
+      <c r="G259" t="s">
+        <v>152</v>
+      </c>
+      <c r="H259" t="s">
+        <v>571</v>
+      </c>
+      <c r="I259" t="s">
+        <v>19</v>
+      </c>
+      <c r="J259" t="s">
+        <v>19</v>
+      </c>
+      <c r="K259" t="s">
+        <v>19</v>
+      </c>
+      <c r="L259" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>572</v>
+      </c>
+      <c r="B260" s="2">
+        <v>46280.855410625</v>
+      </c>
+      <c r="C260" t="s">
+        <v>568</v>
+      </c>
+      <c r="D260" t="s">
+        <v>550</v>
+      </c>
+      <c r="E260" t="s">
+        <v>15</v>
+      </c>
+      <c r="F260" t="s">
+        <v>142</v>
+      </c>
+      <c r="G260" t="s">
+        <v>155</v>
+      </c>
+      <c r="H260" t="s">
+        <v>573</v>
+      </c>
+      <c r="I260" t="s">
+        <v>19</v>
+      </c>
+      <c r="J260" t="s">
+        <v>19</v>
+      </c>
+      <c r="K260" t="s">
+        <v>19</v>
+      </c>
+      <c r="L260" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>574</v>
+      </c>
+      <c r="B261" s="2">
+        <v>46280.85541326389</v>
+      </c>
+      <c r="C261" t="s">
+        <v>568</v>
+      </c>
+      <c r="D261" t="s">
+        <v>550</v>
+      </c>
+      <c r="E261" t="s">
+        <v>15</v>
+      </c>
+      <c r="F261" t="s">
+        <v>16</v>
+      </c>
+      <c r="G261" t="s">
+        <v>152</v>
+      </c>
+      <c r="H261" t="s">
+        <v>575</v>
+      </c>
+      <c r="I261" t="s">
+        <v>19</v>
+      </c>
+      <c r="J261" t="s">
+        <v>19</v>
+      </c>
+      <c r="K261" t="s">
+        <v>19</v>
+      </c>
+      <c r="L261" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>576</v>
+      </c>
+      <c r="B262" s="2">
+        <v>46280.85541592592</v>
+      </c>
+      <c r="C262" t="s">
+        <v>568</v>
+      </c>
+      <c r="D262" t="s">
+        <v>550</v>
+      </c>
+      <c r="E262" t="s">
+        <v>15</v>
+      </c>
+      <c r="F262" t="s">
+        <v>142</v>
+      </c>
+      <c r="G262" t="s">
+        <v>155</v>
+      </c>
+      <c r="H262" t="s">
+        <v>577</v>
+      </c>
+      <c r="I262" t="s">
+        <v>19</v>
+      </c>
+      <c r="J262" t="s">
+        <v>19</v>
+      </c>
+      <c r="K262" t="s">
+        <v>19</v>
+      </c>
+      <c r="L262" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>578</v>
+      </c>
+      <c r="B263" s="2">
+        <v>46280.8554190162</v>
+      </c>
+      <c r="C263" t="s">
+        <v>579</v>
+      </c>
+      <c r="D263" t="s">
+        <v>550</v>
+      </c>
+      <c r="E263" t="s">
+        <v>15</v>
+      </c>
+      <c r="F263" t="s">
+        <v>16</v>
+      </c>
+      <c r="G263" t="s">
+        <v>152</v>
+      </c>
+      <c r="H263" t="s">
+        <v>580</v>
+      </c>
+      <c r="I263" t="s">
+        <v>19</v>
+      </c>
+      <c r="J263" t="s">
+        <v>19</v>
+      </c>
+      <c r="K263" t="s">
+        <v>19</v>
+      </c>
+      <c r="L263" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>581</v>
+      </c>
+      <c r="B264" s="2">
+        <v>46280.85542229167</v>
+      </c>
+      <c r="C264" t="s">
+        <v>579</v>
+      </c>
+      <c r="D264" t="s">
+        <v>550</v>
+      </c>
+      <c r="E264" t="s">
+        <v>15</v>
+      </c>
+      <c r="F264" t="s">
+        <v>142</v>
+      </c>
+      <c r="G264" t="s">
+        <v>155</v>
+      </c>
+      <c r="H264" t="s">
+        <v>582</v>
+      </c>
+      <c r="I264" t="s">
+        <v>19</v>
+      </c>
+      <c r="J264" t="s">
+        <v>19</v>
+      </c>
+      <c r="K264" t="s">
+        <v>19</v>
+      </c>
+      <c r="L264" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>583</v>
+      </c>
+      <c r="B265" s="2">
+        <v>46280.855424988426</v>
+      </c>
+      <c r="C265" t="s">
+        <v>579</v>
+      </c>
+      <c r="D265" t="s">
+        <v>550</v>
+      </c>
+      <c r="E265" t="s">
+        <v>15</v>
+      </c>
+      <c r="F265" t="s">
+        <v>16</v>
+      </c>
+      <c r="G265" t="s">
+        <v>152</v>
+      </c>
+      <c r="H265" t="s">
+        <v>584</v>
+      </c>
+      <c r="I265" t="s">
+        <v>19</v>
+      </c>
+      <c r="J265" t="s">
+        <v>19</v>
+      </c>
+      <c r="K265" t="s">
+        <v>19</v>
+      </c>
+      <c r="L265" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>585</v>
+      </c>
+      <c r="B266" s="2">
+        <v>46280.855428738425</v>
+      </c>
+      <c r="C266" t="s">
+        <v>586</v>
+      </c>
+      <c r="D266" t="s">
+        <v>550</v>
+      </c>
+      <c r="E266" t="s">
+        <v>15</v>
+      </c>
+      <c r="F266" t="s">
+        <v>142</v>
+      </c>
+      <c r="G266" t="s">
+        <v>155</v>
+      </c>
+      <c r="H266" t="s">
+        <v>587</v>
+      </c>
+      <c r="I266" t="s">
+        <v>19</v>
+      </c>
+      <c r="J266" t="s">
+        <v>19</v>
+      </c>
+      <c r="K266" t="s">
+        <v>19</v>
+      </c>
+      <c r="L266" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>588</v>
+      </c>
+      <c r="B267" s="2">
+        <v>46280.85543265047</v>
+      </c>
+      <c r="C267" t="s">
+        <v>586</v>
+      </c>
+      <c r="D267" t="s">
+        <v>550</v>
+      </c>
+      <c r="E267" t="s">
+        <v>15</v>
+      </c>
+      <c r="F267" t="s">
+        <v>16</v>
+      </c>
+      <c r="G267" t="s">
+        <v>152</v>
+      </c>
+      <c r="H267" t="s">
+        <v>589</v>
+      </c>
+      <c r="I267" t="s">
+        <v>19</v>
+      </c>
+      <c r="J267" t="s">
+        <v>19</v>
+      </c>
+      <c r="K267" t="s">
+        <v>19</v>
+      </c>
+      <c r="L267" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>590</v>
+      </c>
+      <c r="B268" s="2">
+        <v>46280.85544346065</v>
+      </c>
+      <c r="C268" t="s">
+        <v>591</v>
+      </c>
+      <c r="D268" t="s">
+        <v>550</v>
+      </c>
+      <c r="E268" t="s">
+        <v>15</v>
+      </c>
+      <c r="F268" t="s">
+        <v>142</v>
+      </c>
+      <c r="G268" t="s">
+        <v>155</v>
+      </c>
+      <c r="H268" t="s">
+        <v>592</v>
+      </c>
+      <c r="I268" t="s">
+        <v>19</v>
+      </c>
+      <c r="J268" t="s">
+        <v>19</v>
+      </c>
+      <c r="K268" t="s">
+        <v>19</v>
+      </c>
+      <c r="L268" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>593</v>
+      </c>
+      <c r="B269" s="2">
+        <v>46280.85544655092</v>
+      </c>
+      <c r="C269" t="s">
+        <v>591</v>
+      </c>
+      <c r="D269" t="s">
+        <v>550</v>
+      </c>
+      <c r="E269" t="s">
+        <v>15</v>
+      </c>
+      <c r="F269" t="s">
+        <v>16</v>
+      </c>
+      <c r="G269" t="s">
+        <v>152</v>
+      </c>
+      <c r="H269" t="s">
+        <v>594</v>
+      </c>
+      <c r="I269" t="s">
+        <v>19</v>
+      </c>
+      <c r="J269" t="s">
+        <v>19</v>
+      </c>
+      <c r="K269" t="s">
+        <v>19</v>
+      </c>
+      <c r="L269" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>595</v>
+      </c>
+      <c r="B270" s="2">
+        <v>46280.85544864583</v>
+      </c>
+      <c r="C270" t="s">
+        <v>591</v>
+      </c>
+      <c r="D270" t="s">
+        <v>550</v>
+      </c>
+      <c r="E270" t="s">
+        <v>15</v>
+      </c>
+      <c r="F270" t="s">
+        <v>142</v>
+      </c>
+      <c r="G270" t="s">
+        <v>155</v>
+      </c>
+      <c r="H270" t="s">
+        <v>596</v>
+      </c>
+      <c r="I270" t="s">
+        <v>19</v>
+      </c>
+      <c r="J270" t="s">
+        <v>19</v>
+      </c>
+      <c r="K270" t="s">
+        <v>19</v>
+      </c>
+      <c r="L270" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>597</v>
+      </c>
+      <c r="B271" s="2">
+        <v>46280.85545216435</v>
+      </c>
+      <c r="C271" t="s">
+        <v>598</v>
+      </c>
+      <c r="D271" t="s">
+        <v>550</v>
+      </c>
+      <c r="E271" t="s">
+        <v>15</v>
+      </c>
+      <c r="F271" t="s">
+        <v>16</v>
+      </c>
+      <c r="G271" t="s">
+        <v>152</v>
+      </c>
+      <c r="H271" t="s">
+        <v>599</v>
+      </c>
+      <c r="I271" t="s">
+        <v>19</v>
+      </c>
+      <c r="J271" t="s">
+        <v>19</v>
+      </c>
+      <c r="K271" t="s">
+        <v>19</v>
+      </c>
+      <c r="L271" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>600</v>
+      </c>
+      <c r="B272" s="2">
+        <v>46280.85546361111</v>
+      </c>
+      <c r="C272" t="s">
+        <v>601</v>
+      </c>
+      <c r="D272" t="s">
+        <v>550</v>
+      </c>
+      <c r="E272" t="s">
+        <v>15</v>
+      </c>
+      <c r="F272" t="s">
+        <v>142</v>
+      </c>
+      <c r="G272" t="s">
+        <v>155</v>
+      </c>
+      <c r="H272" t="s">
+        <v>602</v>
+      </c>
+      <c r="I272" t="s">
+        <v>19</v>
+      </c>
+      <c r="J272" t="s">
+        <v>19</v>
+      </c>
+      <c r="K272" t="s">
+        <v>19</v>
+      </c>
+      <c r="L272" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>603</v>
+      </c>
+      <c r="B273" s="2">
+        <v>46280.855467430556</v>
+      </c>
+      <c r="C273" t="s">
+        <v>601</v>
+      </c>
+      <c r="D273" t="s">
+        <v>550</v>
+      </c>
+      <c r="E273" t="s">
+        <v>15</v>
+      </c>
+      <c r="F273" t="s">
+        <v>16</v>
+      </c>
+      <c r="G273" t="s">
+        <v>152</v>
+      </c>
+      <c r="H273" t="s">
+        <v>604</v>
+      </c>
+      <c r="I273" t="s">
+        <v>19</v>
+      </c>
+      <c r="J273" t="s">
+        <v>19</v>
+      </c>
+      <c r="K273" t="s">
+        <v>19</v>
+      </c>
+      <c r="L273" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>605</v>
+      </c>
+      <c r="B274" s="2">
+        <v>46280.855469780094</v>
+      </c>
+      <c r="C274" t="s">
+        <v>601</v>
+      </c>
+      <c r="D274" t="s">
+        <v>550</v>
+      </c>
+      <c r="E274" t="s">
+        <v>15</v>
+      </c>
+      <c r="F274" t="s">
+        <v>142</v>
+      </c>
+      <c r="G274" t="s">
+        <v>155</v>
+      </c>
+      <c r="H274" t="s">
+        <v>606</v>
+      </c>
+      <c r="I274" t="s">
+        <v>19</v>
+      </c>
+      <c r="J274" t="s">
+        <v>19</v>
+      </c>
+      <c r="K274" t="s">
+        <v>19</v>
+      </c>
+      <c r="L274" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>607</v>
+      </c>
+      <c r="B275" s="2">
+        <v>46280.855472407406</v>
+      </c>
+      <c r="C275" t="s">
+        <v>601</v>
+      </c>
+      <c r="D275" t="s">
+        <v>550</v>
+      </c>
+      <c r="E275" t="s">
+        <v>15</v>
+      </c>
+      <c r="F275" t="s">
+        <v>16</v>
+      </c>
+      <c r="G275" t="s">
+        <v>152</v>
+      </c>
+      <c r="H275" t="s">
+        <v>608</v>
+      </c>
+      <c r="I275" t="s">
+        <v>19</v>
+      </c>
+      <c r="J275" t="s">
+        <v>19</v>
+      </c>
+      <c r="K275" t="s">
+        <v>19</v>
+      </c>
+      <c r="L275" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>609</v>
+      </c>
+      <c r="B276" s="2">
+        <v>46280.85547471065</v>
+      </c>
+      <c r="C276" t="s">
+        <v>610</v>
+      </c>
+      <c r="D276" t="s">
+        <v>550</v>
+      </c>
+      <c r="E276" t="s">
+        <v>15</v>
+      </c>
+      <c r="F276" t="s">
+        <v>142</v>
+      </c>
+      <c r="G276" t="s">
+        <v>155</v>
+      </c>
+      <c r="H276" t="s">
+        <v>611</v>
+      </c>
+      <c r="I276" t="s">
+        <v>19</v>
+      </c>
+      <c r="J276" t="s">
+        <v>19</v>
+      </c>
+      <c r="K276" t="s">
+        <v>19</v>
+      </c>
+      <c r="L276" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11586,7 +12766,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>612</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11614,7 +12794,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>613</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11623,13 +12803,13 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>550</v>
+        <v>614</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>551</v>
+        <v>615</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>552</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -11645,7 +12825,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>553</v>
+        <v>617</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11654,7 +12834,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>554</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -11670,7 +12850,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>555</v>
+        <v>619</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11679,10 +12859,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>556</v>
+        <v>620</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>557</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>
